--- a/SeleniumTests/TestDataFolder/BusinessEntityTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/BusinessEntityTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09011F69-5F2D-4397-B43F-D530389A0EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46924F51-A63D-4871-AB20-8992DFF23CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1PartialMandatoryFieldsTestData" sheetId="6" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="42">
   <si>
     <t>Perindustrian 555</t>
   </si>
@@ -56,39 +56,9 @@
     <t>yanshen.choo@qubeapps.com</t>
   </si>
   <si>
-    <t>MSIC</t>
-  </si>
-  <si>
     <t>yanshen.choo@quapps.com</t>
   </si>
   <si>
-    <t xml:space="preserve"> City</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> State</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pos Code</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Address1</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Address2</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Address3</t>
-  </si>
-  <si>
-    <t>ContactNumber</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>01234567890</t>
   </si>
   <si>
@@ -98,24 +68,6 @@
     <t>TT1</t>
   </si>
   <si>
-    <t>Tourism Tax Register Number</t>
-  </si>
-  <si>
-    <t>SST</t>
-  </si>
-  <si>
-    <t>Register ID</t>
-  </si>
-  <si>
-    <t>Register Type</t>
-  </si>
-  <si>
-    <t>Tin Number</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>SST1</t>
   </si>
   <si>
@@ -140,9 +92,6 @@
     <t>invalid</t>
   </si>
   <si>
-    <t>File Path</t>
-  </si>
-  <si>
     <t>D:\\e-invoice\\SeleniumTests\\InvalidFileType\\TestInvalidFileType.txt</t>
   </si>
   <si>
@@ -153,6 +102,63 @@
   </si>
   <si>
     <t>D:\\e-invoice\\SeleniumTests\\InvalidFileType\\TestInvalidFileType.xlsx</t>
+  </si>
+  <si>
+    <t>Business Entity Name</t>
+  </si>
+  <si>
+    <t>Business Entity Tin Number</t>
+  </si>
+  <si>
+    <t>Business Entity Register ID</t>
+  </si>
+  <si>
+    <t>Business Entity SST</t>
+  </si>
+  <si>
+    <t>Business Entity Tourism Tax Register Number</t>
+  </si>
+  <si>
+    <t>Business Entity Register Type (BRN/NRIC/PASSPORT/ARMY)</t>
+  </si>
+  <si>
+    <t>Business Entity MSIC</t>
+  </si>
+  <si>
+    <t>Business Entity Contact Number</t>
+  </si>
+  <si>
+    <t>Business Entity Email</t>
+  </si>
+  <si>
+    <t>Business Entity City</t>
+  </si>
+  <si>
+    <t>Business Entity State</t>
+  </si>
+  <si>
+    <t>Business Entity Pos Code</t>
+  </si>
+  <si>
+    <t>Business Entity Country</t>
+  </si>
+  <si>
+    <t>Business Entity Address1</t>
+  </si>
+  <si>
+    <t>Business Entity Address2</t>
+  </si>
+  <si>
+    <t>Business Entity Address3</t>
+  </si>
+  <si>
+    <t>Import File Path</t>
+  </si>
+  <si>
+    <t>Business Entity ContactNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Business Entity City</t>
   </si>
 </sst>
 </file>
@@ -487,12 +493,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -504,78 +510,94 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD2BA872-FDAD-4312-92A6-AAFEAFBDE608}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1"/>
     </row>
@@ -588,84 +610,100 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDCA3757-0F4C-4BAC-AED6-3557553F4116}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
@@ -698,81 +736,97 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B064331-C365-4BEB-A79A-2CA00A89F687}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>6</v>
@@ -812,101 +866,99 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" t="s">
         <v>5</v>
@@ -939,72 +991,86 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF41067A-3147-4461-86D5-101EC356BC3E}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
         <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>34</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -1037,69 +1103,83 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D144880A-FFD9-4A78-8A45-88779174BFDA}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
@@ -1138,30 +1218,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8388DD-07AF-4303-9A90-81739344BCD2}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1173,72 +1256,87 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0AB2C8E-533C-4967-8715-031077D1F16C}">
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="66.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="M1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="N1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="O1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>6</v>
@@ -1265,27 +1363,27 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>6</v>
@@ -1312,27 +1410,27 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>6</v>
@@ -1359,27 +1457,27 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>6</v>
@@ -1406,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
